--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
@@ -420,7 +420,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.8888888888888888</v>
+        <v>0.9655172413793104</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -429,16 +429,16 @@
         <v>0.7394366197183099</v>
       </c>
       <c r="D2">
-        <v>0.3394495412844037</v>
+        <v>0.3057851239669421</v>
       </c>
       <c r="E2">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Qwen3-4B-Instruct-2507/metrics_default_vs_aae.xlsx
@@ -420,7 +420,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.9655172413793104</v>
+        <v>0.9770114942528736</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -429,16 +429,16 @@
         <v>0.7394366197183099</v>
       </c>
       <c r="D2">
-        <v>0.3057851239669421</v>
+        <v>0.3032786885245902</v>
       </c>
       <c r="E2">
         <v>87</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
